--- a/3er-semestre/desarrollo-proyecto-i/tareas/Actividad_Referencias/Tabla_Referencias_CarlosPulidoRosas.xlsx
+++ b/3er-semestre/desarrollo-proyecto-i/tareas/Actividad_Referencias/Tabla_Referencias_CarlosPulidoRosas.xlsx
@@ -292,7 +292,7 @@
     <t>Con datos de exportaciones por municipio, sector y destino entre 2004 y 2014, analiza cómo la automatización en Estados Unidos llega a México a través del comercio. El efecto agregado sobre el empleo manufacturero es nulo porque combina pérdidas en unas zonas y ganancias en otras. Es clave para la tesis porque muestra que la presión robótica sobre la manufactura mexicana depende de la composición ocupacional de cada territorio.</t>
   </si>
   <si>
-    <t>Presenta de forma accesible el marco teórico de los mismos autores y lo aplica a datos sectoriales. Explica por qué el empleo puede estancarse aunque la productividad crezca, cuando se automatiza mucho y se crean pocas tareas nuevas. La tesis lo usa para interpretar la prueba de la hipótesis H4, en la que los sectores con mayor incentivo a automatizar profundizaron su capital y perdieron participación laboral.</t>
+    <t>Presenta de forma accesible el marco teórico de los mismos autores y lo aplica a datos sectoriales. Explica por qué el empleo puede estancarse aunque la productividad crezca, cuando se automatiza mucho y se crean pocas tareas nuevas. La tesis lo usa para interpretar la prueba de la hipótesis de rentabilidad, en la que los sectores con mayor incentivo a automatizar profundizaron su capital y perdieron participación laboral.</t>
   </si>
   <si>
     <t>A diferencia de Graetz y Michaels, encuentra efectos negativos y significativos de los robots sobre el empleo local. Mide la exposición de cada zona según su composición industrial, una lógica similar a la del mapa municipal de la tesis, que combina la composición sectorial de los 125 municipios de Jalisco con la exposición de cada sector.</t>
